--- a/python/data/NPA_TABLE.xlsx
+++ b/python/data/NPA_TABLE.xlsx
@@ -1,30 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nasty\Desktop\climate_measures\python\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06BDE76-9A13-4C3E-8932-686EEEE6C9CD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
-  <si>
-    <t xml:space="preserve">Дата опубликования</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="75">
+  <si>
+    <t>Дата опубликования</t>
   </si>
   <si>
     <t>№</t>
   </si>
   <si>
-    <t xml:space="preserve">Вид НПА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Орган гос власти</t>
+    <t>Вид НПА</t>
+  </si>
+  <si>
+    <t>Орган гос власти</t>
   </si>
   <si>
     <t>Название</t>
@@ -39,7 +46,7 @@
     <t>Распоряжение</t>
   </si>
   <si>
-    <t xml:space="preserve">Правительство РФ</t>
+    <t>Правительство РФ</t>
   </si>
   <si>
     <t xml:space="preserve">Национальный план мероприятий первого этапа адаптации </t>
@@ -60,22 +67,22 @@
     <t>Приказ</t>
   </si>
   <si>
-    <t xml:space="preserve">Минэкономразвития РФ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">О внесении изменений в приказ Минэкономразвития России от 13 мая 2021 г. № 267 «Об утверждении методических рекомендаций и показателей по вопросам адаптации к изменениям климата»</t>
+    <t>Минэкономразвития РФ</t>
+  </si>
+  <si>
+    <t>О внесении изменений в приказ Минэкономразвития России от 13 мая 2021 г. № 267 «Об утверждении методических рекомендаций и показателей по вопросам адаптации к изменениям климата»</t>
   </si>
   <si>
     <t>https://www.economy.gov.ru/material/file/8aac7ad23f8dc9bde976bf79f2a2712c/928_28122023.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">Об утверждении Методических рекомендаций по оценке возможного ущерба от воздействия климатических рисков, в том числе рекомендаций по формированию перечня климатически уязвимых объектов в отраслях экономики, в субъектах Российской Федерации и Методических рекомендаций по мониторингу и оценке эффективности и результативности мер по адаптации к изменениям климата</t>
+    <t>Об утверждении Методических рекомендаций по оценке возможного ущерба от воздействия климатических рисков, в том числе рекомендаций по формированию перечня климатически уязвимых объектов в отраслях экономики, в субъектах Российской Федерации и Методических рекомендаций по мониторингу и оценке эффективности и результативности мер по адаптации к изменениям климата</t>
   </si>
   <si>
     <t>https://www.economy.gov.ru/material/file/dca586286823949d756e95b1fd6fe137/927_28122023.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">Об утверждении методических рекомендаций и показателей по вопросам адаптации к изменениям климата</t>
+    <t>Об утверждении методических рекомендаций и показателей по вопросам адаптации к изменениям климата</t>
   </si>
   <si>
     <t>https://www.economy.gov.ru/material/file/b3cc582c24e7367170b5605f1199c6a9/267_13052021.pdf</t>
@@ -84,10 +91,10 @@
     <t>Указ</t>
   </si>
   <si>
-    <t xml:space="preserve">Президент РФ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Об утверждении Климатической доктрины Российской Федерации</t>
+    <t>Президент РФ</t>
+  </si>
+  <si>
+    <t>Об утверждении Климатической доктрины Российской Федерации</t>
   </si>
   <si>
     <t>http://www.kremlin.ru/acts/bank/49910</t>
@@ -96,13 +103,13 @@
     <t>296-ФЗ</t>
   </si>
   <si>
-    <t xml:space="preserve">Федеральный закон</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Федеральное собрание</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Об ограничении выбросов парниковых газов</t>
+    <t>Федеральный закон</t>
+  </si>
+  <si>
+    <t>Федеральное собрание</t>
+  </si>
+  <si>
+    <t>Об ограничении выбросов парниковых газов</t>
   </si>
   <si>
     <t>http://www.kremlin.ru/acts/bank/47013</t>
@@ -111,40 +118,40 @@
     <t>7-ФЗ</t>
   </si>
   <si>
-    <t xml:space="preserve">Об охране окружающей среды</t>
+    <t>Об охране окружающей среды</t>
   </si>
   <si>
     <t>http://pravo.gov.ru/proxy/ips/?docbody=&amp;nd=102074303</t>
   </si>
   <si>
-    <t xml:space="preserve">03.06.2006 (ред. от 29.12.2025)</t>
+    <t>03.06.2006 (ред. от 29.12.2025)</t>
   </si>
   <si>
     <t>74-ФЗ</t>
   </si>
   <si>
-    <t xml:space="preserve">Водный кодекс Российской Федерации</t>
+    <t>Водный кодекс Российской Федерации</t>
   </si>
   <si>
     <t>http://pravo.gov.ru/proxy/ips/?docbody=&amp;nd=102107048</t>
   </si>
   <si>
-    <t xml:space="preserve">04.12.2006 (ред. от 29.12.2025)</t>
+    <t>04.12.2006 (ред. от 29.12.2025)</t>
   </si>
   <si>
     <t>200-ФЗ</t>
   </si>
   <si>
-    <t xml:space="preserve">Лесной кодекс Российской Федерации</t>
+    <t>Лесной кодекс Российской Федерации</t>
   </si>
   <si>
     <t>http://pravo.gov.ru/proxy/ips/?docbody=&amp;nd=102110364</t>
   </si>
   <si>
-    <t xml:space="preserve">МЧС России</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Об утверждении отраслевого плана адаптации к изменениям климата в области гражданской обороны, защиты населения и территорий от чрезвычайных ситуаций природного и техногенного характера</t>
+    <t>МЧС России</t>
+  </si>
+  <si>
+    <t>Об утверждении отраслевого плана адаптации к изменениям климата в области гражданской обороны, защиты населения и территорий от чрезвычайных ситуаций природного и техногенного характера</t>
   </si>
   <si>
     <t>https://mchs.gov.ru/uploads/document/2021-11-18/b28dd5919a2b54654464d34e1ffa14ed.pdf</t>
@@ -156,7 +163,7 @@
     <t>ГОСТ</t>
   </si>
   <si>
-    <t xml:space="preserve">Эвакуация населения, материальных и культурных ценностей в безопасные районы</t>
+    <t>Эвакуация населения, материальных и культурных ценностей в безопасные районы</t>
   </si>
   <si>
     <t>https://docs.cntd.ru/document/1310453202</t>
@@ -165,7 +172,7 @@
     <t>22.3.05-2022</t>
   </si>
   <si>
-    <t xml:space="preserve">Первоочередное жизнеобеспечение пострадавшего населения</t>
+    <t>Первоочередное жизнеобеспечение пострадавшего населения</t>
   </si>
   <si>
     <t>https://docs.cntd.ru/document/1200183497?marker=7D20K3</t>
@@ -174,7 +181,7 @@
     <t>22.3.17-2020</t>
   </si>
   <si>
-    <t xml:space="preserve">Планирование мероприятий по эвакуации и рассредоточению населения при угрозе и возникновении чрезвычайных ситуаций</t>
+    <t>Планирование мероприятий по эвакуации и рассредоточению населения при угрозе и возникновении чрезвычайных ситуаций</t>
   </si>
   <si>
     <t>https://docs.cntd.ru/document/566430562?marker=7D20K3</t>
@@ -183,44 +190,119 @@
     <t>22.0.06-2023</t>
   </si>
   <si>
-    <t xml:space="preserve">Безопасность в чрезвычайных ситуациях. Источники природных чрезвычайных ситуаций. Поражающие факторы. Номенклатура параметров поражающих воздействий</t>
+    <t>Безопасность в чрезвычайных ситуациях. Источники природных чрезвычайных ситуаций. Поражающие факторы. Номенклатура параметров поражающих воздействий</t>
   </si>
   <si>
     <t>https://docs.cntd.ru/document/1302181185</t>
+  </si>
+  <si>
+    <t>input_file</t>
+  </si>
+  <si>
+    <t>1.pdf</t>
+  </si>
+  <si>
+    <t>3.pdf</t>
+  </si>
+  <si>
+    <t>4.pdf</t>
+  </si>
+  <si>
+    <t>6.pdf</t>
+  </si>
+  <si>
+    <t>7.pdf</t>
+  </si>
+  <si>
+    <t>8.pdf</t>
+  </si>
+  <si>
+    <t>9.pdf</t>
+  </si>
+  <si>
+    <t>10.pdf</t>
+  </si>
+  <si>
+    <t>11.pdf</t>
+  </si>
+  <si>
+    <t>12.pdf</t>
+  </si>
+  <si>
+    <t>13.pdf</t>
+  </si>
+  <si>
+    <t>14.pdf</t>
+  </si>
+  <si>
+    <t>15.pdf</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>2.pdf</t>
+  </si>
+  <si>
+    <t>5.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12.000000"/>
-      <color indexed="64"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12.000000"/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12.000000"/>
+      <sz val="12"/>
+      <color indexed="64"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF020C22"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -234,36 +316,38 @@
   </fills>
   <borders count="1">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -274,295 +358,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -765,348 +569,444 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col customWidth="1" min="1" max="2" style="2" width="21.6640625"/>
-    <col customWidth="1" min="3" max="3" style="1" width="25"/>
-    <col customWidth="1" min="4" max="4" style="1" width="27.5546875"/>
-    <col customWidth="1" min="5" max="5" style="1" width="43.109375"/>
-    <col customWidth="1" min="6" max="6" style="1" width="60.5546875"/>
-    <col customWidth="1" min="7" max="7" width="11.44140625"/>
-    <col customWidth="1" min="8" max="8" style="1" width="9.6640625"/>
-    <col min="9" max="16384" style="1" width="9.109375"/>
+    <col min="1" max="1" width="9.1328125" style="1"/>
+    <col min="2" max="3" width="21.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.53125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="43.1328125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="60.53125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.46484375" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" ht="33">
-      <c r="A2" s="3">
+      <c r="H1" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3">
         <v>43824</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" ht="33">
-      <c r="A3" s="3">
+      <c r="H2" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3">
         <v>44996</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" ht="99">
-      <c r="A4" s="3">
+      <c r="H3" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="78.75" x14ac:dyDescent="0.5">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
         <v>45288</v>
       </c>
-      <c r="B4" s="2">
+      <c r="C4" s="2">
         <v>928</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" ht="194.25" customHeight="1">
-      <c r="A5" s="3">
+      <c r="H4" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="194.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
         <v>45288</v>
       </c>
-      <c r="B5" s="2">
+      <c r="C5" s="2">
         <v>927</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" ht="49.5">
-      <c r="A6" s="3">
+      <c r="H5" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="47.25" x14ac:dyDescent="0.5">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
         <v>44329</v>
       </c>
-      <c r="B6" s="2">
+      <c r="C6" s="2">
         <v>267</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" ht="33">
-      <c r="A7" s="3">
+      <c r="H6" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3">
         <v>45225</v>
       </c>
-      <c r="B7" s="2">
+      <c r="C7" s="2">
         <v>812</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" ht="33">
-      <c r="A8" s="3">
+      <c r="H7" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3">
         <v>44379</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="9" ht="16.5">
-      <c r="A9" s="3">
+      <c r="H8" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3">
         <v>37266</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="10" ht="33">
-      <c r="A10" s="3" t="s">
+      <c r="H9" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="11" ht="33">
-      <c r="A11" s="3" t="s">
+      <c r="H10" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="12" ht="99">
-      <c r="A12" s="3">
+      <c r="H11" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="78.75" x14ac:dyDescent="0.5">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3">
         <v>44488</v>
       </c>
-      <c r="B12" s="2">
+      <c r="C12" s="2">
         <v>706</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="13" ht="49.5">
-      <c r="A13" s="3">
+      <c r="H12" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3">
         <v>45778</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="14" ht="33">
-      <c r="A14" s="3">
+      <c r="H13" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3">
         <v>44713</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="15" ht="49.5">
-      <c r="A15" s="3">
+      <c r="H14" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="47.25" x14ac:dyDescent="0.5">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3">
         <v>44348</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="16" ht="82.5">
-      <c r="A16" s="3">
+      <c r="H15" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="78.75" x14ac:dyDescent="0.5">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3">
         <v>45323</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="17" ht="78"/>
+      <c r="H16" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>